--- a/docs/Milestone/CST-452_Sprint_Backlog_SecureLink.xlsx
+++ b/docs/Milestone/CST-452_Sprint_Backlog_SecureLink.xlsx
@@ -1237,7 +1237,7 @@
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>so that my session token survives restarts securely (planned — see AuthToken TODO in ApiClient.cs)</t>
+          <t>so that my session token survives restarts securely</t>
         </is>
       </c>
       <c r="F27" s="8" t="n">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t>so that I know the tunnel is down instead of assuming I'm still protected (planned — see IsHandshakeActive TODO)</t>
+          <t>so that I know the tunnel is down instead of assuming I'm still protected</t>
         </is>
       </c>
       <c r="F28" s="8" t="n">
@@ -1312,7 +1312,7 @@
       <c r="C31" s="6" t="n"/>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>23 of 25 = 92%  (US-24 and US-25 are partially complete)</t>
+          <t>23 of 25 = 92% at Milestone 4; 25 of 25 = 100% after Milestone 6 (US-24 and US-25 completed)</t>
         </is>
       </c>
       <c r="E31" s="7" t="n"/>
@@ -1329,7 +1329,7 @@
       <c r="C32" s="6" t="n"/>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>~90%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="E32" s="7" t="n"/>
